--- a/output/yearly_total_coral_cover_iteration_59_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_59_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.267521143757095</v>
+        <v>1.2569575384594</v>
       </c>
       <c r="C3" t="n">
-        <v>4.696314716283218</v>
+        <v>4.621701890760461</v>
       </c>
       <c r="D3" t="n">
-        <v>6.12313598162939</v>
+        <v>6.049190744545521</v>
       </c>
       <c r="E3" t="n">
-        <v>12.0869718416697</v>
+        <v>11.92785017376538</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.417439942296495</v>
+        <v>1.395260093248812</v>
       </c>
       <c r="C4" t="n">
-        <v>5.33198842387413</v>
+        <v>5.086085654117666</v>
       </c>
       <c r="D4" t="n">
-        <v>6.354856062304263</v>
+        <v>6.233338541357577</v>
       </c>
       <c r="E4" t="n">
-        <v>13.10428442847489</v>
+        <v>12.71468428872405</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.621172588998465</v>
+        <v>1.588448227571783</v>
       </c>
       <c r="C5" t="n">
-        <v>6.163374934219378</v>
+        <v>5.662888085088483</v>
       </c>
       <c r="D5" t="n">
-        <v>6.663835831133118</v>
+        <v>6.523438621584871</v>
       </c>
       <c r="E5" t="n">
-        <v>14.44838335435096</v>
+        <v>13.77477493424514</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.856929107017267</v>
+        <v>1.804189747410806</v>
       </c>
       <c r="C6" t="n">
-        <v>7.189720694223441</v>
+        <v>6.329356680947466</v>
       </c>
       <c r="D6" t="n">
-        <v>6.96288175258495</v>
+        <v>6.827626039207701</v>
       </c>
       <c r="E6" t="n">
-        <v>16.00953155382566</v>
+        <v>14.96117246756597</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.124515225831259</v>
+        <v>2.043857972190433</v>
       </c>
       <c r="C7" t="n">
-        <v>8.365246279443626</v>
+        <v>7.137283324301357</v>
       </c>
       <c r="D7" t="n">
-        <v>7.326767879786915</v>
+        <v>7.20428405481935</v>
       </c>
       <c r="E7" t="n">
-        <v>17.8165293850618</v>
+        <v>16.38542535131114</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.344131822089348</v>
+        <v>1.253777935176055</v>
       </c>
       <c r="C8" t="n">
-        <v>5.939191631469947</v>
+        <v>4.753542194916014</v>
       </c>
       <c r="D8" t="n">
-        <v>5.531945479063991</v>
+        <v>5.489725314799894</v>
       </c>
       <c r="E8" t="n">
-        <v>12.81526893262329</v>
+        <v>11.49704544489196</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.689417288663176</v>
+        <v>1.573742896926787</v>
       </c>
       <c r="C9" t="n">
-        <v>7.292049438419159</v>
+        <v>5.763485488637763</v>
       </c>
       <c r="D9" t="n">
-        <v>5.93863578607801</v>
+        <v>5.985472704193127</v>
       </c>
       <c r="E9" t="n">
-        <v>14.92010251316035</v>
+        <v>13.32270108975768</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.035088226935803</v>
+        <v>1.915446543051862</v>
       </c>
       <c r="C10" t="n">
-        <v>8.824562712103734</v>
+        <v>6.923896925419066</v>
       </c>
       <c r="D10" t="n">
-        <v>6.391935577061817</v>
+        <v>6.470520271308042</v>
       </c>
       <c r="E10" t="n">
-        <v>17.25158651610136</v>
+        <v>15.30986373977897</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.390022051816462</v>
+        <v>2.278619577568143</v>
       </c>
       <c r="C11" t="n">
-        <v>10.52689378955366</v>
+        <v>8.21454863921082</v>
       </c>
       <c r="D11" t="n">
-        <v>6.869903723404379</v>
+        <v>6.953536824137035</v>
       </c>
       <c r="E11" t="n">
-        <v>19.7868195647745</v>
+        <v>17.446705040916</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.74104972608916</v>
+        <v>2.655651465726061</v>
       </c>
       <c r="C12" t="n">
-        <v>12.39096216930841</v>
+        <v>9.600041726863886</v>
       </c>
       <c r="D12" t="n">
-        <v>7.270788267446999</v>
+        <v>7.485333371402466</v>
       </c>
       <c r="E12" t="n">
-        <v>22.40280016284457</v>
+        <v>19.74102656399241</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.069308655215524</v>
+        <v>3.038431510758491</v>
       </c>
       <c r="C13" t="n">
-        <v>14.32184219807602</v>
+        <v>11.02370679245787</v>
       </c>
       <c r="D13" t="n">
-        <v>7.642226169268747</v>
+        <v>8.016214233387068</v>
       </c>
       <c r="E13" t="n">
-        <v>25.03337702256029</v>
+        <v>22.07835253660343</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.756120840925567</v>
+        <v>1.767577836634127</v>
       </c>
       <c r="C14" t="n">
-        <v>10.14540041064062</v>
+        <v>7.793800499704155</v>
       </c>
       <c r="D14" t="n">
-        <v>5.796326803166551</v>
+        <v>6.131112587791755</v>
       </c>
       <c r="E14" t="n">
-        <v>17.69784805473274</v>
+        <v>15.69249092413004</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.798679603904666</v>
+        <v>1.836967764370292</v>
       </c>
       <c r="C15" t="n">
-        <v>11.14127546435155</v>
+        <v>8.36243858748095</v>
       </c>
       <c r="D15" t="n">
-        <v>5.743263339752011</v>
+        <v>6.159710898416465</v>
       </c>
       <c r="E15" t="n">
-        <v>18.68321840800822</v>
+        <v>16.35911725026771</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.080333202776034</v>
+        <v>2.164380623736603</v>
       </c>
       <c r="C16" t="n">
-        <v>13.25037387486201</v>
+        <v>9.872935970281006</v>
       </c>
       <c r="D16" t="n">
-        <v>6.075094063787433</v>
+        <v>6.647629689950088</v>
       </c>
       <c r="E16" t="n">
-        <v>21.40580114142548</v>
+        <v>18.6849462839677</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.665348448190907</v>
+        <v>1.754284972718626</v>
       </c>
       <c r="C17" t="n">
-        <v>12.22895374588659</v>
+        <v>9.115674696087272</v>
       </c>
       <c r="D17" t="n">
-        <v>5.552146514166284</v>
+        <v>6.192177294995907</v>
       </c>
       <c r="E17" t="n">
-        <v>19.44644870824378</v>
+        <v>17.06213696380181</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.881617649959437</v>
+        <v>2.04145599368786</v>
       </c>
       <c r="C18" t="n">
-        <v>14.30198274574303</v>
+        <v>10.66262437114601</v>
       </c>
       <c r="D18" t="n">
-        <v>5.898124222619903</v>
+        <v>6.632019901452563</v>
       </c>
       <c r="E18" t="n">
-        <v>22.08172461832237</v>
+        <v>19.33610026628644</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.869159271592545</v>
+        <v>2.086154966662217</v>
       </c>
       <c r="C19" t="n">
-        <v>15.30053797068654</v>
+        <v>11.43351230347469</v>
       </c>
       <c r="D19" t="n">
-        <v>5.922677732703115</v>
+        <v>6.740424482955497</v>
       </c>
       <c r="E19" t="n">
-        <v>23.0923749749822</v>
+        <v>20.26009175309241</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.057703918193145</v>
+        <v>2.366542110995106</v>
       </c>
       <c r="C20" t="n">
-        <v>17.56526302727421</v>
+        <v>13.27782354067275</v>
       </c>
       <c r="D20" t="n">
-        <v>6.214894936872179</v>
+        <v>7.189593692602497</v>
       </c>
       <c r="E20" t="n">
-        <v>25.83786188233953</v>
+        <v>22.83395934427035</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.210494919336317</v>
+        <v>1.434019236639231</v>
       </c>
       <c r="C21" t="n">
-        <v>12.87718212004667</v>
+        <v>9.888840283089804</v>
       </c>
       <c r="D21" t="n">
-        <v>5.138909270494716</v>
+        <v>5.99867482248886</v>
       </c>
       <c r="E21" t="n">
-        <v>19.2265863098777</v>
+        <v>17.32153434221789</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_59_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_59_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.2569575384594</v>
+        <v>1.26002059129665</v>
       </c>
       <c r="C3" t="n">
-        <v>4.621701890760461</v>
+        <v>4.610293982437113</v>
       </c>
       <c r="D3" t="n">
-        <v>6.049190744545521</v>
+        <v>6.118894831547045</v>
       </c>
       <c r="E3" t="n">
-        <v>11.92785017376538</v>
+        <v>11.98920940528081</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.395260093248812</v>
+        <v>1.392549743984418</v>
       </c>
       <c r="C4" t="n">
-        <v>5.086085654117666</v>
+        <v>5.083026310029927</v>
       </c>
       <c r="D4" t="n">
-        <v>6.233338541357577</v>
+        <v>6.498762610315662</v>
       </c>
       <c r="E4" t="n">
-        <v>12.71468428872405</v>
+        <v>12.97433866433001</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.588448227571783</v>
+        <v>1.576458451401999</v>
       </c>
       <c r="C5" t="n">
-        <v>5.662888085088483</v>
+        <v>5.659619139787849</v>
       </c>
       <c r="D5" t="n">
-        <v>6.523438621584871</v>
+        <v>6.829200805431018</v>
       </c>
       <c r="E5" t="n">
-        <v>13.77477493424514</v>
+        <v>14.06527839662087</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.804189747410806</v>
+        <v>1.790792816188647</v>
       </c>
       <c r="C6" t="n">
-        <v>6.329356680947466</v>
+        <v>6.371072502842662</v>
       </c>
       <c r="D6" t="n">
-        <v>6.827626039207701</v>
+        <v>7.297580192918394</v>
       </c>
       <c r="E6" t="n">
-        <v>14.96117246756597</v>
+        <v>15.4594455119497</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.043857972190433</v>
+        <v>2.03379673626738</v>
       </c>
       <c r="C7" t="n">
-        <v>7.137283324301357</v>
+        <v>7.178119548583166</v>
       </c>
       <c r="D7" t="n">
-        <v>7.20428405481935</v>
+        <v>7.794611536030546</v>
       </c>
       <c r="E7" t="n">
-        <v>16.38542535131114</v>
+        <v>17.00652782088109</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.253777935176055</v>
+        <v>1.257802786223825</v>
       </c>
       <c r="C8" t="n">
-        <v>4.753542194916014</v>
+        <v>4.770305322581204</v>
       </c>
       <c r="D8" t="n">
-        <v>5.489725314799894</v>
+        <v>6.053555376662927</v>
       </c>
       <c r="E8" t="n">
-        <v>11.49704544489196</v>
+        <v>12.08166348546796</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.573742896926787</v>
+        <v>1.577278600552974</v>
       </c>
       <c r="C9" t="n">
-        <v>5.763485488637763</v>
+        <v>5.705250259588827</v>
       </c>
       <c r="D9" t="n">
-        <v>5.985472704193127</v>
+        <v>6.644482788371251</v>
       </c>
       <c r="E9" t="n">
-        <v>13.32270108975768</v>
+        <v>13.92701164851305</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.915446543051862</v>
+        <v>1.914497383616862</v>
       </c>
       <c r="C10" t="n">
-        <v>6.923896925419066</v>
+        <v>6.7272828023126</v>
       </c>
       <c r="D10" t="n">
-        <v>6.470520271308042</v>
+        <v>7.217926581824354</v>
       </c>
       <c r="E10" t="n">
-        <v>15.30986373977897</v>
+        <v>15.85970676775382</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.278619577568143</v>
+        <v>2.269294376228225</v>
       </c>
       <c r="C11" t="n">
-        <v>8.21454863921082</v>
+        <v>7.854584704949797</v>
       </c>
       <c r="D11" t="n">
-        <v>6.953536824137035</v>
+        <v>7.787207347947423</v>
       </c>
       <c r="E11" t="n">
-        <v>17.446705040916</v>
+        <v>17.91108642912545</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.655651465726061</v>
+        <v>2.637733000221931</v>
       </c>
       <c r="C12" t="n">
-        <v>9.600041726863886</v>
+        <v>9.075627423057266</v>
       </c>
       <c r="D12" t="n">
-        <v>7.485333371402466</v>
+        <v>8.400148123424877</v>
       </c>
       <c r="E12" t="n">
-        <v>19.74102656399241</v>
+        <v>20.11350854670408</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.038431510758491</v>
+        <v>3.0176814973576</v>
       </c>
       <c r="C13" t="n">
-        <v>11.02370679245787</v>
+        <v>10.43031211871171</v>
       </c>
       <c r="D13" t="n">
-        <v>8.016214233387068</v>
+        <v>8.95374907412684</v>
       </c>
       <c r="E13" t="n">
-        <v>22.07835253660343</v>
+        <v>22.40174269019615</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.767577836634127</v>
+        <v>1.752380382172387</v>
       </c>
       <c r="C14" t="n">
-        <v>7.793800499704155</v>
+        <v>7.501799280030024</v>
       </c>
       <c r="D14" t="n">
-        <v>6.131112587791755</v>
+        <v>6.771742234720969</v>
       </c>
       <c r="E14" t="n">
-        <v>15.69249092413004</v>
+        <v>16.02592189692338</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.836967764370292</v>
+        <v>1.822153191513208</v>
       </c>
       <c r="C15" t="n">
-        <v>8.36243858748095</v>
+        <v>8.05961850810602</v>
       </c>
       <c r="D15" t="n">
-        <v>6.159710898416465</v>
+        <v>6.836969552191127</v>
       </c>
       <c r="E15" t="n">
-        <v>16.35911725026771</v>
+        <v>16.71874125181035</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.164380623736603</v>
+        <v>2.13998419328607</v>
       </c>
       <c r="C16" t="n">
-        <v>9.872935970281006</v>
+        <v>9.543589067937329</v>
       </c>
       <c r="D16" t="n">
-        <v>6.647629689950088</v>
+        <v>7.42644032625204</v>
       </c>
       <c r="E16" t="n">
-        <v>18.6849462839677</v>
+        <v>19.11001358747544</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.754284972718626</v>
+        <v>1.73075248024783</v>
       </c>
       <c r="C17" t="n">
-        <v>9.115674696087272</v>
+        <v>8.837712468583874</v>
       </c>
       <c r="D17" t="n">
-        <v>6.192177294995907</v>
+        <v>6.961779137832026</v>
       </c>
       <c r="E17" t="n">
-        <v>17.06213696380181</v>
+        <v>17.53024408666373</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2.04145599368786</v>
+        <v>1.988667419630509</v>
       </c>
       <c r="C18" t="n">
-        <v>10.66262437114601</v>
+        <v>10.30783056830826</v>
       </c>
       <c r="D18" t="n">
-        <v>6.632019901452563</v>
+        <v>7.495977516143842</v>
       </c>
       <c r="E18" t="n">
-        <v>19.33610026628644</v>
+        <v>19.79247550408261</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2.086154966662217</v>
+        <v>2.010000797243792</v>
       </c>
       <c r="C19" t="n">
-        <v>11.43351230347469</v>
+        <v>11.02267052420149</v>
       </c>
       <c r="D19" t="n">
-        <v>6.740424482955497</v>
+        <v>7.653184776024883</v>
       </c>
       <c r="E19" t="n">
-        <v>20.26009175309241</v>
+        <v>20.68585609747016</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.366542110995106</v>
+        <v>2.256831805045525</v>
       </c>
       <c r="C20" t="n">
-        <v>13.27782354067275</v>
+        <v>12.67558022897959</v>
       </c>
       <c r="D20" t="n">
-        <v>7.189593692602497</v>
+        <v>8.207774054153907</v>
       </c>
       <c r="E20" t="n">
-        <v>22.83395934427035</v>
+        <v>23.14018608817902</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.434019236639231</v>
+        <v>1.349667473890345</v>
       </c>
       <c r="C21" t="n">
-        <v>9.888840283089804</v>
+        <v>9.357449703212133</v>
       </c>
       <c r="D21" t="n">
-        <v>5.99867482248886</v>
+        <v>6.87627873026917</v>
       </c>
       <c r="E21" t="n">
-        <v>17.32153434221789</v>
+        <v>17.58339590737165</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_59_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_59_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.26002059129665</v>
+        <v>2.619420206538529</v>
       </c>
       <c r="C3" t="n">
-        <v>4.610293982437113</v>
+        <v>7.674839299737073</v>
       </c>
       <c r="D3" t="n">
-        <v>6.118894831547045</v>
+        <v>8.135858839875249</v>
       </c>
       <c r="E3" t="n">
-        <v>11.98920940528081</v>
+        <v>18.43011834615085</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.392549743984418</v>
+        <v>1.122852022926391</v>
       </c>
       <c r="C4" t="n">
-        <v>5.083026310029927</v>
+        <v>4.417795375139354</v>
       </c>
       <c r="D4" t="n">
-        <v>6.498762610315662</v>
+        <v>5.78580297035204</v>
       </c>
       <c r="E4" t="n">
-        <v>12.97433866433001</v>
+        <v>11.32645036841778</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.576458451401999</v>
+        <v>1.249575013729216</v>
       </c>
       <c r="C5" t="n">
-        <v>5.659619139787849</v>
+        <v>4.981664038301451</v>
       </c>
       <c r="D5" t="n">
-        <v>6.829200805431018</v>
+        <v>6.066654689937554</v>
       </c>
       <c r="E5" t="n">
-        <v>14.06527839662087</v>
+        <v>12.29789374196822</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.790792816188647</v>
+        <v>1.393845343165254</v>
       </c>
       <c r="C6" t="n">
-        <v>6.371072502842662</v>
+        <v>5.702870751912474</v>
       </c>
       <c r="D6" t="n">
-        <v>7.297580192918394</v>
+        <v>6.347625460670808</v>
       </c>
       <c r="E6" t="n">
-        <v>15.4594455119497</v>
+        <v>13.44434155574854</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.03379673626738</v>
+        <v>1.54211618985387</v>
       </c>
       <c r="C7" t="n">
-        <v>7.178119548583166</v>
+        <v>6.579041606606258</v>
       </c>
       <c r="D7" t="n">
-        <v>7.794611536030546</v>
+        <v>6.678726114942031</v>
       </c>
       <c r="E7" t="n">
-        <v>17.00652782088109</v>
+        <v>14.79988391140216</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.257802786223825</v>
+        <v>1.694984858612538</v>
       </c>
       <c r="C8" t="n">
-        <v>4.770305322581204</v>
+        <v>7.610358691463489</v>
       </c>
       <c r="D8" t="n">
-        <v>6.053555376662927</v>
+        <v>7.064798194984768</v>
       </c>
       <c r="E8" t="n">
-        <v>12.08166348546796</v>
+        <v>16.3701417450608</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.577278600552974</v>
+        <v>1.846169357095787</v>
       </c>
       <c r="C9" t="n">
-        <v>5.705250259588827</v>
+        <v>8.812375265819421</v>
       </c>
       <c r="D9" t="n">
-        <v>6.644482788371251</v>
+        <v>7.456570910934432</v>
       </c>
       <c r="E9" t="n">
-        <v>13.92701164851305</v>
+        <v>18.11511553384964</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.914497383616862</v>
+        <v>1.139671639951952</v>
       </c>
       <c r="C10" t="n">
-        <v>6.7272828023126</v>
+        <v>6.60272454995784</v>
       </c>
       <c r="D10" t="n">
-        <v>7.217926581824354</v>
+        <v>5.869682991627873</v>
       </c>
       <c r="E10" t="n">
-        <v>15.85970676775382</v>
+        <v>13.61207918153766</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.269294376228225</v>
+        <v>1.076221285826481</v>
       </c>
       <c r="C11" t="n">
-        <v>7.854584704949797</v>
+        <v>7.037844949957067</v>
       </c>
       <c r="D11" t="n">
-        <v>7.787207347947423</v>
+        <v>5.715754769079014</v>
       </c>
       <c r="E11" t="n">
-        <v>17.91108642912545</v>
+        <v>13.82982100486256</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.637733000221931</v>
+        <v>1.167867434017921</v>
       </c>
       <c r="C12" t="n">
-        <v>9.075627423057266</v>
+        <v>8.417926967724979</v>
       </c>
       <c r="D12" t="n">
-        <v>8.400148123424877</v>
+        <v>6.097291379380453</v>
       </c>
       <c r="E12" t="n">
-        <v>20.11350854670408</v>
+        <v>15.68308578112335</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.0176814973576</v>
+        <v>0.9227544846986195</v>
       </c>
       <c r="C13" t="n">
-        <v>10.43031211871171</v>
+        <v>8.133279038355658</v>
       </c>
       <c r="D13" t="n">
-        <v>8.95374907412684</v>
+        <v>5.551763632561627</v>
       </c>
       <c r="E13" t="n">
-        <v>22.40174269019615</v>
+        <v>14.60779715561591</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.752380382172387</v>
+        <v>1.008146900014007</v>
       </c>
       <c r="C14" t="n">
-        <v>7.501799280030024</v>
+        <v>9.663539002442205</v>
       </c>
       <c r="D14" t="n">
-        <v>6.771742234720969</v>
+        <v>5.877900219912418</v>
       </c>
       <c r="E14" t="n">
-        <v>16.02592189692338</v>
+        <v>16.54958612236863</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.822153191513208</v>
+        <v>0.9791951602157687</v>
       </c>
       <c r="C15" t="n">
-        <v>8.05961850810602</v>
+        <v>10.58250394100243</v>
       </c>
       <c r="D15" t="n">
-        <v>6.836969552191127</v>
+        <v>5.906881412141785</v>
       </c>
       <c r="E15" t="n">
-        <v>16.71874125181035</v>
+        <v>17.46858051335998</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.13998419328607</v>
+        <v>1.076771064540859</v>
       </c>
       <c r="C16" t="n">
-        <v>9.543589067937329</v>
+        <v>12.45071091732186</v>
       </c>
       <c r="D16" t="n">
-        <v>7.42644032625204</v>
+        <v>6.309594320423827</v>
       </c>
       <c r="E16" t="n">
-        <v>19.11001358747544</v>
+        <v>19.83707630228654</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.73075248024783</v>
+        <v>0.652253539747496</v>
       </c>
       <c r="C17" t="n">
-        <v>8.837712468583874</v>
+        <v>9.407293034156746</v>
       </c>
       <c r="D17" t="n">
-        <v>6.961779137832026</v>
+        <v>5.234236972577083</v>
       </c>
       <c r="E17" t="n">
-        <v>17.53024408666373</v>
+        <v>15.29378354648133</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.988667419630509</v>
+        <v>0.5149757582626644</v>
       </c>
       <c r="C18" t="n">
-        <v>10.30783056830826</v>
+        <v>8.478598975847431</v>
       </c>
       <c r="D18" t="n">
-        <v>7.495977516143842</v>
+        <v>4.732986047219788</v>
       </c>
       <c r="E18" t="n">
-        <v>19.79247550408261</v>
+        <v>13.72656078132988</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2.010000797243792</v>
+        <v>0.6057579684743669</v>
       </c>
       <c r="C19" t="n">
-        <v>11.02267052420149</v>
+        <v>10.5219301076504</v>
       </c>
       <c r="D19" t="n">
-        <v>7.653184776024883</v>
+        <v>5.207651244746079</v>
       </c>
       <c r="E19" t="n">
-        <v>20.68585609747016</v>
+        <v>16.33533932087085</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.256831805045525</v>
+        <v>0.6942036191499621</v>
       </c>
       <c r="C20" t="n">
-        <v>12.67558022897959</v>
+        <v>12.68324767854975</v>
       </c>
       <c r="D20" t="n">
-        <v>8.207774054153907</v>
+        <v>5.661788097776569</v>
       </c>
       <c r="E20" t="n">
-        <v>23.14018608817902</v>
+        <v>19.03923939547629</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.349667473890345</v>
+        <v>0.7829928815220437</v>
       </c>
       <c r="C21" t="n">
-        <v>9.357449703212133</v>
+        <v>14.86484815701884</v>
       </c>
       <c r="D21" t="n">
-        <v>6.87627873026917</v>
+        <v>6.078589085614551</v>
       </c>
       <c r="E21" t="n">
-        <v>17.58339590737165</v>
+        <v>21.72643012415544</v>
       </c>
     </row>
   </sheetData>
